--- a/www/terminologies/CodeSystem-condition-clinical-supplement-fr.xlsx
+++ b/www/terminologies/CodeSystem-condition-clinical-supplement-fr.xlsx
@@ -105,7 +105,7 @@
     <t>Supplements</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/condition-clinical|3.0.0</t>
+    <t>http://terminology.hl7.org/CodeSystem/condition-clinical</t>
   </si>
   <si>
     <t>Count</t>

--- a/www/terminologies/CodeSystem-condition-clinical-supplement-fr.xlsx
+++ b/www/terminologies/CodeSystem-condition-clinical-supplement-fr.xlsx
@@ -105,7 +105,7 @@
     <t>Supplements</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/condition-clinical</t>
+    <t>http://terminology.hl7.org/CodeSystem/condition-clinical|3.0.0</t>
   </si>
   <si>
     <t>Count</t>
